--- a/3_elektrik_enerjisinin_brut_uretimi_ve_sektorel_tuketimi.xlsx
+++ b/3_elektrik_enerjisinin_brut_uretimi_ve_sektorel_tuketimi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/istemiberk/Library/CloudStorage/GoogleDrive-istemiberk@gmail.com/My Drive/Calismalar/0. Projects/1. In Progress/1001-100. yıl VEdiger/IP1/elektrik veri tahmin/Tuketim/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/istemiberk/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7616B1E4-FB90-B347-BB59-D8BCCD521918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CD1D2B-98EF-BF47-8427-5CC51FA33247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17160" activeTab="1" xr2:uid="{C3577245-A4D5-4D30-B13F-C791A1539AFB}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="1923-1971" sheetId="10" r:id="rId1"/>
     <sheet name="1972-2023" sheetId="8" r:id="rId2"/>
     <sheet name="Tüketim Sektörleri" sheetId="7" r:id="rId3"/>
+    <sheet name="Açıklama" sheetId="11" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
   <si>
     <t>İthalat (+)</t>
   </si>
@@ -165,6 +166,30 @@
   <si>
     <t>Motorlu Kara Taşıtları İmalatı (29)</t>
   </si>
+  <si>
+    <t>Net Üretim=Çevrim ve Enerji Sektörü</t>
+  </si>
+  <si>
+    <t>Elektrik Arzı=Nihai Tüketim</t>
+  </si>
+  <si>
+    <t>(-) Petrol Rafinerileri Tüketimi</t>
+  </si>
+  <si>
+    <t>(-) İç Tüketim ve Kayıp</t>
+  </si>
+  <si>
+    <t>(=) Çevrim ve Enerji Sektörü                        (Net Üretim)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(+) İthalat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-) İhracat </t>
+  </si>
+  <si>
+    <t>(=) Elektrik Arzı                                                        (Nihai Tüketim)</t>
+  </si>
 </sst>
 </file>
 
@@ -253,7 +278,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -302,6 +327,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -314,7 +354,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -389,6 +429,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7857,37 +7903,37 @@
         <v>20337.630705</v>
       </c>
       <c r="AA27" s="14">
-        <v>21284.613361000007</v>
+        <v>18882</v>
       </c>
       <c r="AB27" s="14">
-        <v>25129.825269000001</v>
+        <v>22622</v>
       </c>
       <c r="AC27" s="14">
-        <v>27898.498002000004</v>
+        <v>25285</v>
       </c>
       <c r="AD27" s="14">
-        <v>27411.827675</v>
+        <v>24693</v>
       </c>
       <c r="AE27" s="14">
-        <v>41654.947281000001</v>
+        <v>24681</v>
       </c>
       <c r="AF27" s="14">
-        <v>28777.374270999997</v>
+        <v>28393</v>
       </c>
       <c r="AG27" s="14">
-        <v>31743.633498000003</v>
+        <v>31352</v>
       </c>
       <c r="AH27" s="14">
-        <v>36290.479058500001</v>
+        <v>35891</v>
       </c>
       <c r="AI27" s="14">
-        <v>34830.514122</v>
+        <v>34424</v>
       </c>
       <c r="AJ27" s="14">
-        <v>41775.336530999994</v>
+        <v>41361</v>
       </c>
       <c r="AK27" s="14">
-        <v>44924.179002500001</v>
+        <v>44502</v>
       </c>
       <c r="AL27" s="14">
         <v>41659.446188681919</v>
@@ -8838,7 +8884,7 @@
         <v>130051.30028205059</v>
       </c>
       <c r="AW34" s="14">
-        <v>139449</v>
+        <v>130449</v>
       </c>
       <c r="AX34" s="15">
         <v>129689.09476909933</v>
@@ -9137,4 +9183,65 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB62AECD-0301-8D4B-9DFD-BF69F8D46315}">
+  <dimension ref="B1:I14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="9" max="9" width="28.83203125" style="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="2:9" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I8" s="33" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I10" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I12" s="33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:9" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>